--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>69563251</v>
       </c>
       <c r="B3" t="n">
-        <v>90232</v>
+        <v>90242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>69563251</v>
       </c>
       <c r="B3" t="n">
-        <v>90242</v>
+        <v>90254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>69563251</v>
       </c>
       <c r="B3" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>56442615</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682395.2794288213</v>
+        <v>682395</v>
       </c>
       <c r="R2" t="n">
-        <v>6689794.301435316</v>
+        <v>6689794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2004-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>69563251</v>
       </c>
       <c r="B3" t="n">
-        <v>90255</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69563251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69563251</v>
+        <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>91443</v>
+        <v>92048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,43 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lindersvik 2 km NNO om Norrskedika, Upl</t>
+          <t>Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682351</v>
+        <v>682420</v>
       </c>
       <c r="R3" t="n">
-        <v>6689782</v>
+        <v>6689801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,17 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-08-20</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-08-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex.</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,18 +877,681 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135738247</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135738004</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91572</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682434</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6689757</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135738004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135738275</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91572</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682425</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6689789</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135738275</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69563251</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lindersvik 2 km NNO om Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682351</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6689782</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2004-08-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2004-08-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/69563251</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135776706</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99252</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682425</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6689789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135776706</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135738314</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>682443</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6689818</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135738314</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135738177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106398</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>682411</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6689766</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135738177</t>
         </is>
       </c>
     </row>
@@ -910,6 +1559,12 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91572</v>
+        <v>91574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91572</v>
+        <v>91574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99252</v>
+        <v>99254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106398</v>
+        <v>106400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91574</v>
+        <v>91576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91574</v>
+        <v>91576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99254</v>
+        <v>99271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106400</v>
+        <v>106420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91576</v>
+        <v>91577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91576</v>
+        <v>91577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106420</v>
+        <v>106422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91577</v>
+        <v>91578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91577</v>
+        <v>91578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106422</v>
+        <v>106423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106423</v>
+        <v>106424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91579</v>
+        <v>91585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91579</v>
+        <v>91585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106424</v>
+        <v>106430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106430</v>
+        <v>106431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91586</v>
+        <v>91592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99281</v>
+        <v>99292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106431</v>
+        <v>106442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9646-2024 artfynd.xlsx
+++ b/artfynd/A 9646-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135738247</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135738004</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135738275</v>
       </c>
       <c r="B5" t="n">
-        <v>91592</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135776706</v>
       </c>
       <c r="B7" t="n">
-        <v>99292</v>
+        <v>99305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135738314</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135738177</v>
       </c>
       <c r="B9" t="n">
-        <v>106442</v>
+        <v>106455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
